--- a/Paladin_CT_sample.xlsx
+++ b/Paladin_CT_sample.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CT_Samples" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Statistics" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +473,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
       <c r="B2" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
       <c r="C2" t="n">
-        <v>6.6</v>
+        <v>61.1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="E2" t="n">
         <v>10.9</v>
@@ -490,36 +491,36 @@
         <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>25.2</v>
+        <v>11.4</v>
       </c>
       <c r="H2" t="n">
-        <v>56.8</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>25.6</v>
+        <v>9.9</v>
       </c>
       <c r="B3" t="n">
-        <v>23.7</v>
+        <v>57</v>
       </c>
       <c r="C3" t="n">
-        <v>6.5</v>
+        <v>10.2</v>
       </c>
       <c r="D3" t="n">
-        <v>11.6</v>
+        <v>20.4</v>
       </c>
       <c r="E3" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>17.6</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>13.9</v>
+        <v>11.4</v>
       </c>
       <c r="H3" t="n">
-        <v>8.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -527,163 +528,163 @@
         <v>10.4</v>
       </c>
       <c r="B4" t="n">
-        <v>13.3</v>
+        <v>10.3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.6</v>
+        <v>10.3</v>
       </c>
       <c r="D4" t="n">
-        <v>11.6</v>
+        <v>21.8</v>
       </c>
       <c r="E4" t="n">
-        <v>14.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>13.8</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>8.4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11.7</v>
+        <v>10.3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.6</v>
+        <v>10.3</v>
       </c>
       <c r="C5" t="n">
-        <v>6.6</v>
+        <v>10.3</v>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="E5" t="n">
-        <v>11.6</v>
+        <v>10.9</v>
       </c>
       <c r="F5" t="n">
-        <v>31.3</v>
+        <v>11.3</v>
       </c>
       <c r="G5" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>9.300000000000001</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>11.9</v>
+        <v>25.2</v>
       </c>
       <c r="B6" t="n">
-        <v>11.9</v>
+        <v>10.3</v>
       </c>
       <c r="C6" t="n">
-        <v>6.5</v>
+        <v>24.3</v>
       </c>
       <c r="D6" t="n">
-        <v>11.7</v>
+        <v>31.5</v>
       </c>
       <c r="E6" t="n">
-        <v>11.6</v>
+        <v>10.9</v>
       </c>
       <c r="F6" t="n">
-        <v>12.3</v>
+        <v>10.9</v>
       </c>
       <c r="G6" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="H6" t="n">
-        <v>75.59999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16.3</v>
+        <v>9.9</v>
       </c>
       <c r="B7" t="n">
-        <v>16.2</v>
+        <v>10.2</v>
       </c>
       <c r="C7" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="D7" t="n">
-        <v>16.3</v>
+        <v>12.3</v>
       </c>
       <c r="E7" t="n">
-        <v>11.9</v>
+        <v>8.9</v>
       </c>
       <c r="F7" t="n">
-        <v>10.9</v>
+        <v>71.2</v>
       </c>
       <c r="G7" t="n">
-        <v>13.9</v>
+        <v>11.3</v>
       </c>
       <c r="H7" t="n">
-        <v>8.4</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>24</v>
+        <v>10.3</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>134.4</v>
       </c>
       <c r="C8" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="D8" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="E8" t="n">
-        <v>23.7</v>
+        <v>10.9</v>
       </c>
       <c r="F8" t="n">
-        <v>11.1</v>
+        <v>27.2</v>
       </c>
       <c r="G8" t="n">
-        <v>11.3</v>
+        <v>166.8</v>
       </c>
       <c r="H8" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>11.5</v>
+        <v>10.3</v>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>10.3</v>
       </c>
       <c r="C9" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="E9" t="n">
-        <v>11.5</v>
+        <v>16.9</v>
       </c>
       <c r="F9" t="n">
-        <v>12.8</v>
+        <v>44.3</v>
       </c>
       <c r="G9" t="n">
-        <v>11.3</v>
+        <v>21.6</v>
       </c>
       <c r="H9" t="n">
-        <v>22.1</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10.4</v>
+        <v>12.2</v>
       </c>
       <c r="B10" t="n">
-        <v>10.4</v>
+        <v>12.2</v>
       </c>
       <c r="C10" t="n">
         <v>6.7</v>
@@ -692,77 +693,2480 @@
         <v>11.7</v>
       </c>
       <c r="E10" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="F10" t="n">
-        <v>29.2</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>13.4</v>
+        <v>11.3</v>
       </c>
       <c r="H10" t="n">
-        <v>8.4</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="B11" t="n">
-        <v>11.7</v>
+        <v>12.5</v>
       </c>
       <c r="C11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="D11" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="E11" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F11" t="n">
         <v>11.5</v>
       </c>
-      <c r="F11" t="n">
-        <v>11.2</v>
-      </c>
       <c r="G11" t="n">
-        <v>11.3</v>
+        <v>27.4</v>
       </c>
       <c r="H11" t="n">
-        <v>9.4</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13.1</v>
+        <v>11.6</v>
       </c>
       <c r="B12" t="n">
-        <v>13.1</v>
+        <v>12.3</v>
       </c>
       <c r="C12" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="D12" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E12" t="n">
         <v>11.7</v>
       </c>
-      <c r="E12" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>13.6</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="A13" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>6.8</v>
+      </c>
       <c r="D13" t="n">
         <v>11.7</v>
       </c>
       <c r="E13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="B14" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="B15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>22</v>
+      </c>
+      <c r="D15" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="B16" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="B17" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>41</v>
+      </c>
+      <c r="B19" t="n">
+        <v>41</v>
+      </c>
+      <c r="C19" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="B20" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="B21" t="n">
+        <v>30</v>
+      </c>
+      <c r="C21" t="n">
+        <v>30</v>
+      </c>
+      <c r="D21" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>11</v>
+      </c>
+      <c r="G21" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="B22" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="C22" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B23" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E23" t="n">
         <v>11.7</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="B24" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>11</v>
+      </c>
+      <c r="G24" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="B25" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C25" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>11</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="B26" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G26" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="B27" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="D27" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H27" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="B28" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>11</v>
+      </c>
+      <c r="G28" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>19</v>
+      </c>
+      <c r="B29" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C29" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>11</v>
+      </c>
+      <c r="G29" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>18</v>
+      </c>
+      <c r="B30" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E30" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>11</v>
+      </c>
+      <c r="G30" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="B31" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="D31" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16</v>
+      </c>
+      <c r="F31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="B32" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>14</v>
+      </c>
+      <c r="F32" t="n">
+        <v>11</v>
+      </c>
+      <c r="G32" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="B33" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>11</v>
+      </c>
+      <c r="G33" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="B34" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="D34" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F34" t="n">
+        <v>11</v>
+      </c>
+      <c r="G34" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B35" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F35" t="n">
+        <v>11</v>
+      </c>
+      <c r="G35" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="B36" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="C36" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>14</v>
+      </c>
+      <c r="G36" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C37" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="F37" t="n">
+        <v>14</v>
+      </c>
+      <c r="G37" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H37" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="B38" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C38" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>12</v>
+      </c>
+      <c r="G38" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="B39" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C39" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>12</v>
+      </c>
+      <c r="E39" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G39" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="B40" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E40" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G40" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H40" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="B41" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C41" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="F41" t="n">
+        <v>12</v>
+      </c>
+      <c r="G41" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H41" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="B42" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="E42" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>12</v>
+      </c>
+      <c r="G42" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H42" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="B43" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="C43" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D43" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E43" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G43" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H43" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="B44" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="C44" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="D44" t="n">
+        <v>110</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F44" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="G44" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="B45" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>110</v>
+      </c>
+      <c r="D45" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E45" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F45" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="G45" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H45" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="B46" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>77</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="G46" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="B47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="C47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="F47" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H47" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="B48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="C48" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="F48" t="n">
+        <v>11</v>
+      </c>
+      <c r="G48" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="H48" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>10</v>
+      </c>
+      <c r="B49" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="C49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D49" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E49" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="F49" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G49" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H49" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="B50" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="C50" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E50" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>17</v>
+      </c>
+      <c r="B51" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D51" t="n">
+        <v>29</v>
+      </c>
+      <c r="E51" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="F51" t="n">
+        <v>11</v>
+      </c>
+      <c r="G51" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="H51" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="B52" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="C52" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="D52" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E52" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H52" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>10</v>
+      </c>
+      <c r="B53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="C53" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="E53" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H53" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="B54" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C54" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>11</v>
+      </c>
+      <c r="G54" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H54" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="B55" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C55" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="E55" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F55" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G55" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H55" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="B56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="C56" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D56" t="n">
+        <v>18</v>
+      </c>
+      <c r="E56" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H56" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="C57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>11</v>
+      </c>
+      <c r="F57" t="n">
+        <v>11</v>
+      </c>
+      <c r="G57" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H57" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="C58" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D58" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="E58" t="n">
+        <v>11</v>
+      </c>
+      <c r="F58" t="n">
+        <v>11</v>
+      </c>
+      <c r="G58" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H58" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="C59" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D59" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F59" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G59" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H59" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B60" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C60" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D60" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E60" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>26</v>
+      </c>
+      <c r="G60" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H60" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="B61" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="C61" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D61" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E61" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="F61" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="G61" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H61" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="B62" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C62" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D62" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E62" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G62" t="n">
+        <v>14</v>
+      </c>
+      <c r="H62" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B63" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D63" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E63" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F63" t="n">
+        <v>11</v>
+      </c>
+      <c r="G63" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H63" t="n">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="C64" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D64" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F64" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="G64" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H64" t="n">
+        <v>126.4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="B65" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C65" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D65" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F65" t="n">
+        <v>59</v>
+      </c>
+      <c r="G65" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H65" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B66" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C66" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D66" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="C67" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D67" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="E67" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F67" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G67" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="B68" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D68" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E68" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F68" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G68" t="n">
+        <v>64</v>
+      </c>
+      <c r="H68" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="B69" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D69" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F69" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G69" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H69" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="B70" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C70" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D70" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E70" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="F70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H70" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="B71" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="C71" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D71" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H71" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="B72" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="C72" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D72" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E72" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="F72" t="n">
+        <v>11</v>
+      </c>
+      <c r="G72" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H72" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="B73" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="C73" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D73" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E73" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G73" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H73" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="B74" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C74" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D74" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E74" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F74" t="n">
+        <v>50</v>
+      </c>
+      <c r="G74" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H74" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="B75" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="C75" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E75" t="n">
+        <v>11</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11</v>
+      </c>
+      <c r="G75" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="H75" t="n">
+        <v>42.7</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B76" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C76" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D76" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E76" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F76" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G76" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H76" t="n">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="B77" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C77" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D77" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E77" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="F77" t="n">
+        <v>11</v>
+      </c>
+      <c r="G77" t="n">
+        <v>13</v>
+      </c>
+      <c r="H77" t="n">
+        <v>38.7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B78" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C78" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D78" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E78" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F78" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G78" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H78" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="B79" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="C79" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D79" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="E79" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F79" t="n">
+        <v>11</v>
+      </c>
+      <c r="G79" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H79" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="B80" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="C80" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D80" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E80" t="n">
+        <v>15</v>
+      </c>
+      <c r="F80" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G80" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="H80" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>12</v>
+      </c>
+      <c r="B81" t="n">
+        <v>12</v>
+      </c>
+      <c r="C81" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D81" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E81" t="n">
+        <v>14</v>
+      </c>
+      <c r="F81" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H81" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="B82" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="C82" t="n">
+        <v>8</v>
+      </c>
+      <c r="D82" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E82" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F82" t="n">
+        <v>11</v>
+      </c>
+      <c r="G82" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H82" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="B83" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="C83" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F83" t="n">
+        <v>18</v>
+      </c>
+      <c r="G83" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H83" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B84" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C84" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F84" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H84" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="B85" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="C85" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F85" t="n">
+        <v>11</v>
+      </c>
+      <c r="G85" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="H85" t="n">
+        <v>82.2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="B86" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C86" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F86" t="n">
+        <v>11</v>
+      </c>
+      <c r="G86" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="H86" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B87" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C87" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F87" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G87" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H87" t="n">
+        <v>63.7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="B88" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C88" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F88" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G88" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H88" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B89" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C89" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="F89" t="n">
+        <v>18</v>
+      </c>
+      <c r="G89" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H89" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="B90" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C90" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F90" t="n">
+        <v>11</v>
+      </c>
+      <c r="G90" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H90" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>11</v>
+      </c>
+      <c r="B91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C91" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H91" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="B92" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="C92" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F92" t="n">
+        <v>43</v>
+      </c>
+      <c r="G92" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H92" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="B93" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C93" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="F93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H93" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="B94" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="C94" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G94" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="B95" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="H95" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="B96" t="n">
+        <v>22</v>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G96" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H96" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>11</v>
+      </c>
+      <c r="G97" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H97" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G98" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H98" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G99" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H99" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G100" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H100" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G101" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H101" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Variance</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Std Dev</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>M1 Gasket</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>19.63052631578948</v>
+      </c>
+      <c r="C2" t="n">
+        <v>299.8253348264278</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.31546519231949</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>M2 PHD</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>20.02210526315789</v>
+      </c>
+      <c r="C3" t="n">
+        <v>410.7440806270996</v>
+      </c>
+      <c r="D3" t="n">
+        <v>20.26682216399748</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>M3 Male IMLA assy</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>14.28279569892473</v>
+      </c>
+      <c r="C4" t="n">
+        <v>273.7429616643291</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16.54517940864737</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>M4 Female IMLA assy</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>21.80246913580247</v>
+      </c>
+      <c r="C5" t="n">
+        <v>389.0879938271605</v>
+      </c>
+      <c r="D5" t="n">
+        <v>19.72531352924867</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>M5 Flatten and welding</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>19.35760869565217</v>
+      </c>
+      <c r="C6" t="n">
+        <v>316.1506008122312</v>
+      </c>
+      <c r="D6" t="n">
+        <v>17.78062430884335</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>M6 Female IMLA assy</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>16.12970297029703</v>
+      </c>
+      <c r="C7" t="n">
+        <v>127.677108910891</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11.29942958342991</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>M7 Female IMLA assy</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>16.52941176470588</v>
+      </c>
+      <c r="C8" t="n">
+        <v>300.474769947583</v>
+      </c>
+      <c r="D8" t="n">
+        <v>17.33420808538951</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>M8 Short/Code</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>18.114</v>
+      </c>
+      <c r="C9" t="n">
+        <v>269.6208121212121</v>
+      </c>
+      <c r="D9" t="n">
+        <v>16.42013435149701</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
